--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
   <si>
     <t/>
   </si>
   <si>
-    <t>20139653</t>
-  </si>
-  <si>
-    <t>LRST FAC.TIS 2X200S</t>
+    <t>20094171</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR 24X200</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,49 +28,88 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20135430</t>
-  </si>
-  <si>
-    <t>LAURIER RN 18'S 35CM</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20080459</t>
-  </si>
-  <si>
-    <t>IDM KACANG KULIT 180</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10036848</t>
-  </si>
-  <si>
-    <t>INDOCAFE CF.MIX30X20</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20020008</t>
-  </si>
-  <si>
-    <t>MR.BREAD MANIS CHO 4</t>
+    <t>20024699</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 62G</t>
+  </si>
+  <si>
+    <t>20125389</t>
+  </si>
+  <si>
+    <t>STT FRCH FRS LVL3 60</t>
+  </si>
+  <si>
+    <t>20094283</t>
+  </si>
+  <si>
+    <t>INDOMILK KM PTH 535G</t>
+  </si>
+  <si>
+    <t>20120855</t>
+  </si>
+  <si>
+    <t>INDOMILK SWIS CHO535</t>
+  </si>
+  <si>
+    <t>20128291</t>
+  </si>
+  <si>
+    <t>IDM KCG ALMD MADU 65</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20104000</t>
+  </si>
+  <si>
+    <t>IDM KACANG ALMOND 65</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20129486</t>
+  </si>
+  <si>
+    <t>MR.BRD ISI KEJU SUSU</t>
   </si>
   <si>
     <t>RT,(E-1H)</t>
@@ -82,9 +121,6 @@
     <t>F/F FULL CRM TPK 225</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
     <t>20034079</t>
   </si>
   <si>
@@ -97,85 +133,112 @@
     <t>F/FLAG STRWB TPK 225</t>
   </si>
   <si>
-    <t>20141062</t>
-  </si>
-  <si>
-    <t>SQ CHUNKY CUPID 3X26</t>
-  </si>
-  <si>
-    <t>20141063</t>
-  </si>
-  <si>
-    <t>SQ CSHW BTRFLY 3X22G</t>
-  </si>
-  <si>
-    <t>10036987</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO CASHEW 52G</t>
-  </si>
-  <si>
-    <t>10003485</t>
-  </si>
-  <si>
-    <t>S/Q CHOCO ALMOND 52G</t>
-  </si>
-  <si>
-    <t>20092857</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 130</t>
-  </si>
-  <si>
-    <t>20119460</t>
-  </si>
-  <si>
-    <t>POTABEE SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20122571</t>
-  </si>
-  <si>
-    <t>PIATTOS SAPI PG 115G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20098348</t>
-  </si>
-  <si>
-    <t>REBO KUACI ORIGNL120</t>
-  </si>
-  <si>
-    <t>20015337</t>
-  </si>
-  <si>
-    <t>LEXUS SANDW COKL 190</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20133506</t>
-  </si>
-  <si>
-    <t>DELFI KRICE SWET64.8</t>
-  </si>
-  <si>
-    <t>20134969</t>
-  </si>
-  <si>
-    <t>MILO SANDW MILK 104G</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600ML</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20003786</t>
+  </si>
+  <si>
+    <t>NU GREEN TEA HNY 450</t>
+  </si>
+  <si>
+    <t>20113059</t>
+  </si>
+  <si>
+    <t>NU YOGURT TEA 450ML</t>
+  </si>
+  <si>
+    <t>20076052</t>
+  </si>
+  <si>
+    <t>PUCUK TEH MLTI 1.3L</t>
+  </si>
+  <si>
+    <t>10004884</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CHO 950</t>
+  </si>
+  <si>
+    <t>10005909</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT PLN 950</t>
+  </si>
+  <si>
+    <t>20134048</t>
+  </si>
+  <si>
+    <t>HILO PRTEIN CHOCO190</t>
+  </si>
+  <si>
+    <t>20080706</t>
+  </si>
+  <si>
+    <t>L-MEN WP 2GO CHO 200</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20100142</t>
+  </si>
+  <si>
+    <t>TEH KOTAK BLCKCR 300</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20139300</t>
+  </si>
+  <si>
+    <t>BROOKFARM MATCHA 200</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
 </sst>
 </file>
@@ -568,14 +631,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -675,15 +739,15 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -695,15 +759,15 @@
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -715,15 +779,15 @@
         <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -735,15 +799,15 @@
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -755,55 +819,55 @@
         <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -812,10 +876,10 @@
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,10 +896,10 @@
         <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -849,13 +913,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -869,21 +933,21 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -892,18 +956,18 @@
         <v>16</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -912,90 +976,290 @@
         <v>16</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>23</v>
+      <c r="F25" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="67">
   <si>
     <t/>
   </si>
   <si>
-    <t>20094171</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR 24X200</t>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,217 +28,190 @@
     <t>1</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20134576</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LEMON650</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>10014263</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL CMR 720</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20090066</t>
+  </si>
+  <si>
+    <t>WIPOL SRH + JRK 720</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20001645</t>
+  </si>
+  <si>
+    <t>WIPOL KARBOL LMN 720</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20009499</t>
+  </si>
+  <si>
+    <t>BIORE BF WHT/S RF380</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20031215</t>
+  </si>
+  <si>
+    <t>BIORE BF LIVELY 400</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20125580</t>
+  </si>
+  <si>
+    <t>JAPOTA NPS PDS 68G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20097774</t>
+  </si>
+  <si>
+    <t>JAPOTA JPN.SEAWD 68G</t>
+  </si>
+  <si>
+    <t>20097776</t>
+  </si>
+  <si>
+    <t>JAPOTA HNY BUTTER 68</t>
+  </si>
+  <si>
+    <t>20004229</t>
+  </si>
+  <si>
+    <t>SMAX RING CHEESE 40G</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20024699</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 62G</t>
-  </si>
-  <si>
-    <t>20125389</t>
-  </si>
-  <si>
-    <t>STT FRCH FRS LVL3 60</t>
-  </si>
-  <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>20128291</t>
-  </si>
-  <si>
-    <t>IDM KCG ALMD MADU 65</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20104000</t>
-  </si>
-  <si>
-    <t>IDM KACANG ALMOND 65</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20129486</t>
-  </si>
-  <si>
-    <t>MR.BRD ISI KEJU SUSU</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/F FULL CRM TPK 225</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG COKLT TPK 225</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STRWB TPK 225</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600ML</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20003786</t>
-  </si>
-  <si>
-    <t>NU GREEN TEA HNY 450</t>
-  </si>
-  <si>
-    <t>20113059</t>
-  </si>
-  <si>
-    <t>NU YOGURT TEA 450ML</t>
-  </si>
-  <si>
-    <t>20076052</t>
-  </si>
-  <si>
-    <t>PUCUK TEH MLTI 1.3L</t>
-  </si>
-  <si>
-    <t>10004884</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CHO 950</t>
-  </si>
-  <si>
-    <t>10005909</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT PLN 950</t>
-  </si>
-  <si>
-    <t>20134048</t>
-  </si>
-  <si>
-    <t>HILO PRTEIN CHOCO190</t>
-  </si>
-  <si>
-    <t>20080706</t>
-  </si>
-  <si>
-    <t>L-MEN WP 2GO CHO 200</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20100142</t>
-  </si>
-  <si>
-    <t>TEH KOTAK BLCKCR 300</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20139295</t>
-  </si>
-  <si>
-    <t>BROOKFARM ORI 200ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20139300</t>
-  </si>
-  <si>
-    <t>BROOKFARM MATCHA 200</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>20113083</t>
+  </si>
+  <si>
+    <t>TESSA FC.TISU 2X200S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20125783</t>
+  </si>
+  <si>
+    <t>CAP/ENAK KKM PTH 535</t>
+  </si>
+  <si>
+    <t>20035829</t>
+  </si>
+  <si>
+    <t>TEBS TEA WT/SODA 500</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>20037974</t>
+  </si>
+  <si>
+    <t>ULTRA UHT MOKA 250</t>
+  </si>
+  <si>
+    <t>20023846</t>
+  </si>
+  <si>
+    <t>PRNGLES ORIGNAL 102G</t>
+  </si>
+  <si>
+    <t>20023845</t>
+  </si>
+  <si>
+    <t>PRINGLES CHEESY 102G</t>
+  </si>
+  <si>
+    <t>20092063</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 115</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20012680</t>
+  </si>
+  <si>
+    <t>QTELA KRPK ORG 175G</t>
+  </si>
+  <si>
+    <t>20138106</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWG 135</t>
+  </si>
+  <si>
+    <t>20052630</t>
+  </si>
+  <si>
+    <t>LOTTE CHOCO PIE 156G</t>
+  </si>
+  <si>
+    <t>20091225</t>
+  </si>
+  <si>
+    <t>OVLTNE CHO BISC 104G</t>
+  </si>
+  <si>
+    <t>10000104</t>
+  </si>
+  <si>
+    <t>REGAL MARIE 120GR</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
   </si>
 </sst>
 </file>
@@ -631,15 +604,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -699,15 +671,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -716,18 +688,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -736,78 +708,78 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -816,18 +788,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -836,18 +808,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -856,410 +828,330 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="94">
   <si>
     <t/>
   </si>
   <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
+    <t>20053796</t>
+  </si>
+  <si>
+    <t>SOKLN SOFTG PRPL 720</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,190 +28,271 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20085113</t>
+  </si>
+  <si>
+    <t>RNSO+ML PWD PRFM 700</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20134576</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LEMON650</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10014263</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL CMR 720</t>
+    <t>20113567</t>
+  </si>
+  <si>
+    <t>GENTLE GEN MR.BRZ700</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20090066</t>
-  </si>
-  <si>
-    <t>WIPOL SRH + JRK 720</t>
+    <t>20115959</t>
+  </si>
+  <si>
+    <t>GENTLE GEN FR.PE 700</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20001645</t>
-  </si>
-  <si>
-    <t>WIPOL KARBOL LMN 720</t>
+    <t>20020245</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI BLUE 765</t>
+  </si>
+  <si>
+    <t>20020226</t>
+  </si>
+  <si>
+    <t>MOLTO PWNGI PINK 765</t>
+  </si>
+  <si>
+    <t>20080360</t>
+  </si>
+  <si>
+    <t>DOWNY MYSTIQUE 550ML</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20080361</t>
+  </si>
+  <si>
+    <t>DOWNY PASSION 550ML</t>
+  </si>
+  <si>
+    <t>20113093</t>
+  </si>
+  <si>
+    <t>ROYALE SUNNY DAY 600</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20009499</t>
-  </si>
-  <si>
-    <t>BIORE BF WHT/S RF380</t>
+    <t>20128706</t>
+  </si>
+  <si>
+    <t>ROYALE LNVDR VNL 600</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>20113917</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC SWT 100</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20031215</t>
-  </si>
-  <si>
-    <t>BIORE BF LIVELY 400</t>
+    <t>20113918</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC FRSH100</t>
+  </si>
+  <si>
+    <t>20135607</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC LVELY100</t>
+  </si>
+  <si>
+    <t>20103266</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C H&amp;F 180</t>
+  </si>
+  <si>
+    <t>20113915</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C SOFT 180</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20125580</t>
-  </si>
-  <si>
-    <t>JAPOTA NPS PDS 68G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20097774</t>
-  </si>
-  <si>
-    <t>JAPOTA JPN.SEAWD 68G</t>
-  </si>
-  <si>
-    <t>20097776</t>
-  </si>
-  <si>
-    <t>JAPOTA HNY BUTTER 68</t>
-  </si>
-  <si>
-    <t>20004229</t>
-  </si>
-  <si>
-    <t>SMAX RING CHEESE 40G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20113083</t>
-  </si>
-  <si>
-    <t>TESSA FC.TISU 2X200S</t>
+    <t>20135637</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B WSH 300</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20052754</t>
+  </si>
+  <si>
+    <t>PIGEON BTL STD 50ML</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>RT</t>
   </si>
   <si>
-    <t>20125783</t>
-  </si>
-  <si>
-    <t>CAP/ENAK KKM PTH 535</t>
-  </si>
-  <si>
-    <t>20035829</t>
-  </si>
-  <si>
-    <t>TEBS TEA WT/SODA 500</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>20037974</t>
-  </si>
-  <si>
-    <t>ULTRA UHT MOKA 250</t>
-  </si>
-  <si>
-    <t>20023846</t>
-  </si>
-  <si>
-    <t>PRNGLES ORIGNAL 102G</t>
-  </si>
-  <si>
-    <t>20023845</t>
-  </si>
-  <si>
-    <t>PRINGLES CHEESY 102G</t>
-  </si>
-  <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20012680</t>
-  </si>
-  <si>
-    <t>QTELA KRPK ORG 175G</t>
-  </si>
-  <si>
-    <t>20138106</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWG 135</t>
-  </si>
-  <si>
-    <t>20052630</t>
-  </si>
-  <si>
-    <t>LOTTE CHOCO PIE 156G</t>
-  </si>
-  <si>
-    <t>20091225</t>
-  </si>
-  <si>
-    <t>OVLTNE CHO BISC 104G</t>
-  </si>
-  <si>
-    <t>10000104</t>
-  </si>
-  <si>
-    <t>REGAL MARIE 120GR</t>
-  </si>
-  <si>
-    <t>20138261</t>
-  </si>
-  <si>
-    <t>POCKY BLUEBERRY 38G</t>
+    <t>20044351</t>
+  </si>
+  <si>
+    <t>SHINZU'I B/CLN KR480</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20011008</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 400</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20060393</t>
+  </si>
+  <si>
+    <t>NUVO CAIR CLSC 400</t>
+  </si>
+  <si>
+    <t>20093101</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS380</t>
+  </si>
+  <si>
+    <t>20009500</t>
+  </si>
+  <si>
+    <t>BIORE B.FOAM RELX400</t>
+  </si>
+  <si>
+    <t>20049941</t>
+  </si>
+  <si>
+    <t>LUX BW MCG ORCHD 400</t>
+  </si>
+  <si>
+    <t>10012742</t>
+  </si>
+  <si>
+    <t>LISTERINE COOLMIN250</t>
+  </si>
+  <si>
+    <t>20137173</t>
+  </si>
+  <si>
+    <t>SCRLETT EDP VEL.R 30</t>
+  </si>
+  <si>
+    <t>20137253</t>
+  </si>
+  <si>
+    <t>BRAVEN EDP COOL 100M</t>
+  </si>
+  <si>
+    <t>20008719</t>
+  </si>
+  <si>
+    <t>F&amp;N HJB PR.CHRMG 100</t>
+  </si>
+  <si>
+    <t>10003511</t>
+  </si>
+  <si>
+    <t>PIERRE DEO PUTIH 150</t>
+  </si>
+  <si>
+    <t>20062306</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO ICE 45</t>
+  </si>
+  <si>
+    <t>20051842</t>
+  </si>
+  <si>
+    <t>NIVEA/M R/ON INVS 50</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20127437</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP HFT 340</t>
+  </si>
+  <si>
+    <t>20075943</t>
+  </si>
+  <si>
+    <t>MKRZO SHP ALOE&amp;M 170</t>
+  </si>
+  <si>
+    <t>20007302</t>
+  </si>
+  <si>
+    <t>MARINA LOT H&amp;GLW 185</t>
+  </si>
+  <si>
+    <t>20021816</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 200</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20083615</t>
+  </si>
+  <si>
+    <t>HRBRST MNYK ZTN 150</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20053183</t>
+  </si>
+  <si>
+    <t>GTSBY STYL POMADE 75</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
 </sst>
 </file>
@@ -604,13 +685,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -671,15 +753,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -688,7 +770,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -696,10 +778,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -708,7 +790,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>5</v>
@@ -716,22 +798,22 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -745,41 +827,41 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -788,18 +870,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -808,18 +890,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -828,130 +910,130 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -965,193 +1047,393 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -175,7 +175,7 @@
     <t>20011008</t>
   </si>
   <si>
-    <t>LIFEBUOY BW RED 400</t>
+    <t>LIFEBUOY BW RED 380</t>
   </si>
   <si>
     <t>PT,(E-3B)</t>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="77">
   <si>
     <t/>
   </si>
   <si>
-    <t>20053796</t>
-  </si>
-  <si>
-    <t>SOKLN SOFTG PRPL 720</t>
+    <t>20112945</t>
+  </si>
+  <si>
+    <t>FF SKM COKLAT 240G</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,271 +28,220 @@
     <t>1</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20118115</t>
+  </si>
+  <si>
+    <t>FRISIAN FLAG PTH 240</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10000861</t>
+  </si>
+  <si>
+    <t>POP MIE BASO 75G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>10014292</t>
+  </si>
+  <si>
+    <t>POP MIE KRI AYM 75G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
+  </si>
+  <si>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20085113</t>
-  </si>
-  <si>
-    <t>RNSO+ML PWD PRFM 700</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20113567</t>
-  </si>
-  <si>
-    <t>GENTLE GEN MR.BRZ700</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20115959</t>
-  </si>
-  <si>
-    <t>GENTLE GEN FR.PE 700</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20020245</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI BLUE 765</t>
-  </si>
-  <si>
-    <t>20020226</t>
-  </si>
-  <si>
-    <t>MOLTO PWNGI PINK 765</t>
-  </si>
-  <si>
-    <t>20080360</t>
-  </si>
-  <si>
-    <t>DOWNY MYSTIQUE 550ML</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20080361</t>
-  </si>
-  <si>
-    <t>DOWNY PASSION 550ML</t>
-  </si>
-  <si>
-    <t>20113093</t>
-  </si>
-  <si>
-    <t>ROYALE SUNNY DAY 600</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20128706</t>
-  </si>
-  <si>
-    <t>ROYALE LNVDR VNL 600</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20113917</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC SWT 100</t>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
+  </si>
+  <si>
+    <t>20062365</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 A/KRM133</t>
+  </si>
+  <si>
+    <t>20084444</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 A.KCP129</t>
+  </si>
+  <si>
+    <t>10035852</t>
+  </si>
+  <si>
+    <t>BIHUNKU GRG SPCL 60G</t>
+  </si>
+  <si>
+    <t>10007415</t>
+  </si>
+  <si>
+    <t>SUN KARA SANTAN 200</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20113918</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC FRSH100</t>
-  </si>
-  <si>
-    <t>20135607</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC LVELY100</t>
-  </si>
-  <si>
-    <t>20103266</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C H&amp;F 180</t>
-  </si>
-  <si>
-    <t>20113915</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C SOFT 180</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20135637</t>
-  </si>
-  <si>
-    <t>MY BABY H&amp;B WSH 300</t>
+    <t>10036806</t>
+  </si>
+  <si>
+    <t>KARA SANTAN 200ML</t>
+  </si>
+  <si>
+    <t>20103453</t>
+  </si>
+  <si>
+    <t>SAORI SAUS LD HTM133</t>
+  </si>
+  <si>
+    <t>20009973</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TERIYK135</t>
+  </si>
+  <si>
+    <t>20009966</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TIRAM 133</t>
+  </si>
+  <si>
+    <t>20066050</t>
+  </si>
+  <si>
+    <t>DELMONTE SPG.SAUS250</t>
+  </si>
+  <si>
+    <t>20066052</t>
+  </si>
+  <si>
+    <t>DLMONTE BBQ.SAUS 250</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20052754</t>
-  </si>
-  <si>
-    <t>PIGEON BTL STD 50ML</t>
+    <t>20049493</t>
+  </si>
+  <si>
+    <t>MAESTRO LGHT MAYO100</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20044351</t>
-  </si>
-  <si>
-    <t>SHINZU'I B/CLN KR480</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20011008</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW RED 380</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20060393</t>
-  </si>
-  <si>
-    <t>NUVO CAIR CLSC 400</t>
-  </si>
-  <si>
-    <t>20093101</t>
-  </si>
-  <si>
-    <t>ZEN BW A.BAC SHIS380</t>
-  </si>
-  <si>
-    <t>20009500</t>
-  </si>
-  <si>
-    <t>BIORE B.FOAM RELX400</t>
-  </si>
-  <si>
-    <t>20049941</t>
-  </si>
-  <si>
-    <t>LUX BW MCG ORCHD 400</t>
-  </si>
-  <si>
-    <t>10012742</t>
-  </si>
-  <si>
-    <t>LISTERINE COOLMIN250</t>
-  </si>
-  <si>
-    <t>20137173</t>
-  </si>
-  <si>
-    <t>SCRLETT EDP VEL.R 30</t>
-  </si>
-  <si>
-    <t>20137253</t>
-  </si>
-  <si>
-    <t>BRAVEN EDP COOL 100M</t>
-  </si>
-  <si>
-    <t>20008719</t>
-  </si>
-  <si>
-    <t>F&amp;N HJB PR.CHRMG 100</t>
-  </si>
-  <si>
-    <t>10003511</t>
-  </si>
-  <si>
-    <t>PIERRE DEO PUTIH 150</t>
-  </si>
-  <si>
-    <t>20062306</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO ICE 45</t>
-  </si>
-  <si>
-    <t>20051842</t>
-  </si>
-  <si>
-    <t>NIVEA/M R/ON INVS 50</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20127437</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP HFT 340</t>
-  </si>
-  <si>
-    <t>20075943</t>
-  </si>
-  <si>
-    <t>MKRZO SHP ALOE&amp;M 170</t>
-  </si>
-  <si>
-    <t>20007302</t>
-  </si>
-  <si>
-    <t>MARINA LOT H&amp;GLW 185</t>
-  </si>
-  <si>
-    <t>20021816</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 200</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20083615</t>
-  </si>
-  <si>
-    <t>HRBRST MNYK ZTN 150</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20053183</t>
-  </si>
-  <si>
-    <t>GTSBY STYL POMADE 75</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>10016646</t>
+  </si>
+  <si>
+    <t>INDO/F KECAP MN.R725</t>
+  </si>
+  <si>
+    <t>10022534</t>
+  </si>
+  <si>
+    <t>ABC KCP MNS PCH685G</t>
+  </si>
+  <si>
+    <t>20027097</t>
+  </si>
+  <si>
+    <t>INDOFOOD SMBL EXT275</t>
+  </si>
+  <si>
+    <t>20015850</t>
+  </si>
+  <si>
+    <t>INDOFOOD SBL PDS 275</t>
+  </si>
+  <si>
+    <t>20064412</t>
+  </si>
+  <si>
+    <t>ABC SAMBAL ASLI 270</t>
+  </si>
+  <si>
+    <t>20063027</t>
+  </si>
+  <si>
+    <t>ABC SMBL EXT.PDS 270</t>
+  </si>
+  <si>
+    <t>20003405</t>
+  </si>
+  <si>
+    <t>FORVITA MARGARINE200</t>
   </si>
 </sst>
 </file>
@@ -685,15 +634,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -730,18 +678,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -750,10 +698,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -773,15 +721,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -790,150 +738,150 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -947,13 +895,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -967,13 +915,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -987,13 +935,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1007,41 +955,41 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1050,390 +998,290 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="61">
   <si>
     <t/>
   </si>
   <si>
-    <t>20112945</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 240G</t>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,220 +28,172 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20118115</t>
-  </si>
-  <si>
-    <t>FRISIAN FLAG PTH 240</t>
+    <t>10014292</t>
+  </si>
+  <si>
+    <t>POP MIE KRI AYM 75G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
+    <t>20094693</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI AYM 5.5K</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20119164</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI YKNKU115</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10000861</t>
-  </si>
-  <si>
-    <t>POP MIE BASO 75G</t>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>10023791</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR.AYAM72</t>
+  </si>
+  <si>
+    <t>20104155</t>
+  </si>
+  <si>
+    <t>NISSIN HOT CARBO 120</t>
+  </si>
+  <si>
+    <t>20031775</t>
+  </si>
+  <si>
+    <t>NISSIN GEKIKARA 109G</t>
+  </si>
+  <si>
+    <t>20009269</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 135</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>10014292</t>
-  </si>
-  <si>
-    <t>POP MIE KRI AYM 75G</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20002415</t>
+  </si>
+  <si>
+    <t>FILMA MARGARN. 200GR</t>
+  </si>
+  <si>
+    <t>10000210</t>
+  </si>
+  <si>
+    <t>BLUE BAND CUP 230G</t>
+  </si>
+  <si>
+    <t>20055496</t>
+  </si>
+  <si>
+    <t>PRO CHIZ SPRD 160G</t>
+  </si>
+  <si>
+    <t>20113341</t>
+  </si>
+  <si>
+    <t>EMINA CHS SLC MOZA5S</t>
+  </si>
+  <si>
+    <t>20088712</t>
+  </si>
+  <si>
+    <t>SASA SANT.KLP CAIR65</t>
+  </si>
+  <si>
+    <t>20087284</t>
+  </si>
+  <si>
+    <t>SASA SANTAN KLP 200</t>
+  </si>
+  <si>
+    <t>20066052</t>
+  </si>
+  <si>
+    <t>DLMONTE BBQ.SAUS 250</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
-  </si>
-  <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
-  </si>
-  <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>20062365</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 A/KRM133</t>
-  </si>
-  <si>
-    <t>20084444</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 A.KCP129</t>
-  </si>
-  <si>
-    <t>10035852</t>
-  </si>
-  <si>
-    <t>BIHUNKU GRG SPCL 60G</t>
-  </si>
-  <si>
-    <t>10007415</t>
-  </si>
-  <si>
-    <t>SUN KARA SANTAN 200</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>10036806</t>
-  </si>
-  <si>
-    <t>KARA SANTAN 200ML</t>
-  </si>
-  <si>
-    <t>20103453</t>
-  </si>
-  <si>
-    <t>SAORI SAUS LD HTM133</t>
-  </si>
-  <si>
-    <t>20009973</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TERIYK135</t>
-  </si>
-  <si>
-    <t>20009966</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TIRAM 133</t>
-  </si>
-  <si>
-    <t>20066050</t>
-  </si>
-  <si>
-    <t>DELMONTE SPG.SAUS250</t>
-  </si>
-  <si>
-    <t>20066052</t>
-  </si>
-  <si>
-    <t>DLMONTE BBQ.SAUS 250</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20049493</t>
-  </si>
-  <si>
-    <t>MAESTRO LGHT MAYO100</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
-    <t>10022534</t>
-  </si>
-  <si>
-    <t>ABC KCP MNS PCH685G</t>
-  </si>
-  <si>
-    <t>20027097</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMBL EXT275</t>
-  </si>
-  <si>
-    <t>20015850</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 275</t>
-  </si>
-  <si>
-    <t>20064412</t>
-  </si>
-  <si>
-    <t>ABC SAMBAL ASLI 270</t>
-  </si>
-  <si>
-    <t>20063027</t>
-  </si>
-  <si>
-    <t>ABC SMBL EXT.PDS 270</t>
-  </si>
-  <si>
-    <t>20003405</t>
-  </si>
-  <si>
-    <t>FORVITA MARGARINE200</t>
+    <t>20040296</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 900</t>
+  </si>
+  <si>
+    <t>20071686</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+ MADU 700G</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SWIZZ CHO 340G</t>
+  </si>
+  <si>
+    <t>20021571</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VAN 560G</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20082394</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ MDU700</t>
+  </si>
+  <si>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DNCOW FRTGO ENR 780G</t>
   </si>
 </sst>
 </file>
@@ -634,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -678,18 +630,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -698,18 +650,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -718,18 +670,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -738,18 +690,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -758,350 +710,350 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1115,173 +1067,33 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
   <si>
     <t/>
   </si>
   <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,172 +28,154 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10004401</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT VAN 180</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10000975</t>
+  </si>
+  <si>
+    <t>POP MIE AYAM 75G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>10014292</t>
-  </si>
-  <si>
-    <t>POP MIE KRI AYM 75G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20094693</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI AYM 5.5K</t>
+    <t>10000861</t>
+  </si>
+  <si>
+    <t>POP MIE BASO 75G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20119164</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI YKNKU115</t>
+    <t>20107729</t>
+  </si>
+  <si>
+    <t>TOP COFF GL AREN 9'S</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>10023791</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR.AYAM72</t>
-  </si>
-  <si>
-    <t>20104155</t>
-  </si>
-  <si>
-    <t>NISSIN HOT CARBO 120</t>
-  </si>
-  <si>
-    <t>20031775</t>
-  </si>
-  <si>
-    <t>NISSIN GEKIKARA 109G</t>
-  </si>
-  <si>
-    <t>20009269</t>
-  </si>
-  <si>
-    <t>DELMONTE EXT.HOT 135</t>
+    <t>RT,(E-5B)</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20126424</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20119036</t>
+  </si>
+  <si>
+    <t>RIN-BEE STK KJU 130G</t>
+  </si>
+  <si>
+    <t>20116110</t>
+  </si>
+  <si>
+    <t>MXCORN ROAST.CR 130G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20116675</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 115</t>
+  </si>
+  <si>
+    <t>20092063</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 115</t>
+  </si>
+  <si>
+    <t>20119437</t>
+  </si>
+  <si>
+    <t>POTABEE BBG 115G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20111641</t>
+  </si>
+  <si>
+    <t>BETTER VANILLA 100G</t>
+  </si>
+  <si>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORIGNL120</t>
+  </si>
+  <si>
+    <t>20093909</t>
+  </si>
+  <si>
+    <t>REBO KUACI MILK 120</t>
+  </si>
+  <si>
+    <t>10000430</t>
+  </si>
+  <si>
+    <t>REGAL MARIE SPC. 230</t>
+  </si>
+  <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20002415</t>
-  </si>
-  <si>
-    <t>FILMA MARGARN. 200GR</t>
-  </si>
-  <si>
-    <t>10000210</t>
-  </si>
-  <si>
-    <t>BLUE BAND CUP 230G</t>
-  </si>
-  <si>
-    <t>20055496</t>
-  </si>
-  <si>
-    <t>PRO CHIZ SPRD 160G</t>
-  </si>
-  <si>
-    <t>20113341</t>
-  </si>
-  <si>
-    <t>EMINA CHS SLC MOZA5S</t>
-  </si>
-  <si>
-    <t>20088712</t>
-  </si>
-  <si>
-    <t>SASA SANT.KLP CAIR65</t>
-  </si>
-  <si>
-    <t>20087284</t>
-  </si>
-  <si>
-    <t>SASA SANTAN KLP 200</t>
-  </si>
-  <si>
-    <t>20066052</t>
-  </si>
-  <si>
-    <t>DLMONTE BBQ.SAUS 250</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20040296</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 900</t>
-  </si>
-  <si>
-    <t>20071686</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+ MADU 700G</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SWIZZ CHO 340G</t>
-  </si>
-  <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 560G</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20082394</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ MDU700</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DNCOW FRTGO ENR 780G</t>
+    <t>20055311</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE WFR 110</t>
+  </si>
+  <si>
+    <t>20055312</t>
+  </si>
+  <si>
+    <t>NBATI RCHCO WFR C110</t>
+  </si>
+  <si>
+    <t>20113383</t>
+  </si>
+  <si>
+    <t>ROMA KLPA FRSH 6'S</t>
   </si>
 </sst>
 </file>
@@ -586,14 +568,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -673,27 +655,27 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -713,55 +695,55 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -770,18 +752,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -790,18 +772,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -810,27 +792,27 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>32</v>
@@ -838,10 +820,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -850,7 +832,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>32</v>
@@ -858,10 +840,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -870,229 +852,149 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
   <si>
     <t/>
   </si>
   <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
+    <t>20138230</t>
+  </si>
+  <si>
+    <t>DORITOS JGG BKR 120G</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -31,151 +31,184 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10004401</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT VAN 180</t>
+    <t>20138231</t>
+  </si>
+  <si>
+    <t>DORITOS SMB SALSA120</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
+    <t>20097774</t>
+  </si>
+  <si>
+    <t>JAPOTA JPN.SEAWD 65G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20097776</t>
+  </si>
+  <si>
+    <t>JAPOTA HNY BUTTER 65</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20116670</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 65G</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
+  </si>
+  <si>
+    <t>20101064</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHEESE 50</t>
+  </si>
+  <si>
+    <t>20101065</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHKN 50</t>
+  </si>
+  <si>
+    <t>20141457</t>
+  </si>
+  <si>
+    <t>PRLGS BR SWD 102</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20033450</t>
+  </si>
+  <si>
+    <t>QTELA KRP/TMPE ORI55</t>
+  </si>
+  <si>
+    <t>20057730</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWNG 70</t>
+  </si>
+  <si>
+    <t>20024699</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 62G</t>
+  </si>
+  <si>
+    <t>10006890</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 40G</t>
+  </si>
+  <si>
+    <t>20024856</t>
+  </si>
+  <si>
+    <t>TAO KAE CLASSIC 3.2G</t>
+  </si>
+  <si>
+    <t>20023148</t>
+  </si>
+  <si>
+    <t>TIC TAC SAPI PNGG 80</t>
+  </si>
+  <si>
+    <t>20056977</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA BWG 95</t>
+  </si>
+  <si>
+    <t>20130152</t>
+  </si>
+  <si>
+    <t>LEMONILO BROWNIES 33</t>
+  </si>
+  <si>
+    <t>20046434</t>
+  </si>
+  <si>
+    <t>BRIO POTATO BISC 56G</t>
+  </si>
+  <si>
+    <t>20106307</t>
+  </si>
+  <si>
+    <t>MR.POTATO GHOST/P 40</t>
+  </si>
+  <si>
+    <t>20120198</t>
+  </si>
+  <si>
+    <t>MR/P GHST/P SWEED40</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20037618</t>
+  </si>
+  <si>
+    <t>ROMA MLKIST ABON 105</t>
+  </si>
+  <si>
+    <t>10000310</t>
+  </si>
+  <si>
+    <t>ROMA SWT MALKIST 105</t>
+  </si>
+  <si>
+    <t>20122975</t>
+  </si>
+  <si>
+    <t>CHOCOLITO RC.CHO 38G</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20057475</t>
+  </si>
+  <si>
+    <t>SERENA TOGO CKLT 128</t>
+  </si>
+  <si>
+    <t>20076573</t>
+  </si>
+  <si>
+    <t>NEXTAR CHO.BRWNS 8'S</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10000861</t>
-  </si>
-  <si>
-    <t>POP MIE BASO 75G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20107729</t>
-  </si>
-  <si>
-    <t>TOP COFF GL AREN 9'S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-5B)</t>
-  </si>
-  <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20045611</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRNG CUP85</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20126424</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20119036</t>
-  </si>
-  <si>
-    <t>RIN-BEE STK KJU 130G</t>
-  </si>
-  <si>
-    <t>20116110</t>
-  </si>
-  <si>
-    <t>MXCORN ROAST.CR 130G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20116675</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 115</t>
-  </si>
-  <si>
-    <t>20092063</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 115</t>
-  </si>
-  <si>
-    <t>20119437</t>
-  </si>
-  <si>
-    <t>POTABEE BBG 115G</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20111641</t>
-  </si>
-  <si>
-    <t>BETTER VANILLA 100G</t>
-  </si>
-  <si>
-    <t>20098348</t>
-  </si>
-  <si>
-    <t>REBO KUACI ORIGNL120</t>
-  </si>
-  <si>
-    <t>20093909</t>
-  </si>
-  <si>
-    <t>REBO KUACI MILK 120</t>
-  </si>
-  <si>
-    <t>10000430</t>
-  </si>
-  <si>
-    <t>REGAL MARIE SPC. 230</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20055311</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE WFR 110</t>
-  </si>
-  <si>
-    <t>20055312</t>
-  </si>
-  <si>
-    <t>NBATI RCHCO WFR C110</t>
-  </si>
-  <si>
-    <t>20113383</t>
-  </si>
-  <si>
-    <t>ROMA KLPA FRSH 6'S</t>
+    <t>20071797</t>
+  </si>
+  <si>
+    <t>NEXTAR PINEAPPLE 8'S</t>
   </si>
 </sst>
 </file>
@@ -568,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -689,61 +722,61 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -752,18 +785,18 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -772,38 +805,38 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -812,18 +845,18 @@
         <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -832,18 +865,18 @@
         <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -852,27 +885,27 @@
         <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -880,10 +913,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -892,7 +925,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -900,10 +933,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -912,7 +945,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -920,82 +953,202 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>5</v>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
   <si>
     <t/>
   </si>
   <si>
-    <t>20138230</t>
-  </si>
-  <si>
-    <t>DORITOS JGG BKR 120G</t>
+    <t>20094171</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR 24X200</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,187 +28,217 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20140679</t>
+  </si>
+  <si>
+    <t>IDM FC.TISSUE 3X80'S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20044199</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG CB.IJO85</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138231</t>
-  </si>
-  <si>
-    <t>DORITOS SMB SALSA120</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20097774</t>
-  </si>
-  <si>
-    <t>JAPOTA JPN.SEAWD 65G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20097776</t>
-  </si>
-  <si>
-    <t>JAPOTA HNY BUTTER 65</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20116670</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 65G</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
-  </si>
-  <si>
-    <t>20101064</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHEESE 50</t>
-  </si>
-  <si>
-    <t>20101065</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHKN 50</t>
-  </si>
-  <si>
-    <t>20141457</t>
-  </si>
-  <si>
-    <t>PRLGS BR SWD 102</t>
+    <t>20009269</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 135</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20033450</t>
-  </si>
-  <si>
-    <t>QTELA KRP/TMPE ORI55</t>
-  </si>
-  <si>
-    <t>20057730</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWNG 70</t>
-  </si>
-  <si>
-    <t>20024699</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 62G</t>
-  </si>
-  <si>
-    <t>10006890</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 40G</t>
-  </si>
-  <si>
-    <t>20024856</t>
-  </si>
-  <si>
-    <t>TAO KAE CLASSIC 3.2G</t>
-  </si>
-  <si>
-    <t>20023148</t>
-  </si>
-  <si>
-    <t>TIC TAC SAPI PNGG 80</t>
-  </si>
-  <si>
-    <t>20056977</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA BWG 95</t>
-  </si>
-  <si>
-    <t>20130152</t>
-  </si>
-  <si>
-    <t>LEMONILO BROWNIES 33</t>
-  </si>
-  <si>
-    <t>20046434</t>
-  </si>
-  <si>
-    <t>BRIO POTATO BISC 56G</t>
-  </si>
-  <si>
-    <t>20106307</t>
-  </si>
-  <si>
-    <t>MR.POTATO GHOST/P 40</t>
-  </si>
-  <si>
-    <t>20120198</t>
-  </si>
-  <si>
-    <t>MR/P GHST/P SWEED40</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20129436</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 RDANG132</t>
+  </si>
+  <si>
+    <t>20062365</t>
+  </si>
+  <si>
+    <t>SUKSES ISI2 A/KRM133</t>
+  </si>
+  <si>
+    <t>20066052</t>
+  </si>
+  <si>
+    <t>DLMONTE BBQ.SAUS 250</t>
+  </si>
+  <si>
+    <t>20066050</t>
+  </si>
+  <si>
+    <t>DELMONTE SPG.SAUS250</t>
+  </si>
+  <si>
+    <t>20134777</t>
+  </si>
+  <si>
+    <t>SASA KARI JPG ORI 40</t>
+  </si>
+  <si>
+    <t>10022118</t>
+  </si>
+  <si>
+    <t>SUN KARA SANTAN KL65</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20037618</t>
-  </si>
-  <si>
-    <t>ROMA MLKIST ABON 105</t>
-  </si>
-  <si>
-    <t>10000310</t>
-  </si>
-  <si>
-    <t>ROMA SWT MALKIST 105</t>
-  </si>
-  <si>
-    <t>20122975</t>
-  </si>
-  <si>
-    <t>CHOCOLITO RC.CHO 38G</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20057475</t>
-  </si>
-  <si>
-    <t>SERENA TOGO CKLT 128</t>
-  </si>
-  <si>
-    <t>20076573</t>
-  </si>
-  <si>
-    <t>NEXTAR CHO.BRWNS 8'S</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20071797</t>
-  </si>
-  <si>
-    <t>NEXTAR PINEAPPLE 8'S</t>
+    <t>20088712</t>
+  </si>
+  <si>
+    <t>SASA SANT.KLP CAIR65</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20132345</t>
+  </si>
+  <si>
+    <t>KELLOG FROT LOOPS 55</t>
+  </si>
+  <si>
+    <t>20134578</t>
+  </si>
+  <si>
+    <t>KELLOGGS COCO FILL60</t>
+  </si>
+  <si>
+    <t>20053052</t>
+  </si>
+  <si>
+    <t>CERES CHO.HZLNUT 180</t>
+  </si>
+  <si>
+    <t>20139438</t>
+  </si>
+  <si>
+    <t>DLMONTE CHO HZL 190G</t>
+  </si>
+  <si>
+    <t>20139437</t>
+  </si>
+  <si>
+    <t>DLMONTE PNUT BTR 170</t>
+  </si>
+  <si>
+    <t>20055265</t>
+  </si>
+  <si>
+    <t>T/J MADU TJ MRNI 150</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20126527</t>
+  </si>
+  <si>
+    <t>KEWPIE MAYO ORGNL 70</t>
+  </si>
+  <si>
+    <t>20003405</t>
+  </si>
+  <si>
+    <t>FORVITA MARGARINE200</t>
+  </si>
+  <si>
+    <t>20138100</t>
+  </si>
+  <si>
+    <t>FVTA MRGN TUB 200G</t>
+  </si>
+  <si>
+    <t>20132727</t>
+  </si>
+  <si>
+    <t>WNCHEZ KJ/CD OLH 170</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20103453</t>
+  </si>
+  <si>
+    <t>SAORI SAUS LD HTM133</t>
+  </si>
+  <si>
+    <t>20009973</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TERIYK135</t>
+  </si>
+  <si>
+    <t>20009966</t>
+  </si>
+  <si>
+    <t>SAORI SAUS TIRAM 133</t>
+  </si>
+  <si>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMN YES HKTA CHKN88G</t>
+  </si>
+  <si>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMN YES TKYO CHKN84G</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
 </sst>
 </file>
@@ -601,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -668,15 +698,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -685,38 +715,38 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -725,10 +755,10 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -745,18 +775,18 @@
         <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -765,390 +795,450 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>63</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,234 +11,288 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="94">
   <si>
     <t/>
   </si>
   <si>
+    <t>20126648</t>
+  </si>
+  <si>
+    <t>LE MINERALE 6X330ML</t>
+  </si>
+  <si>
+    <t>EG1A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
     <t>20094171</t>
   </si>
   <si>
     <t>INDOMARET AIR 24X200</t>
   </si>
   <si>
-    <t>EG1A</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20140679</t>
-  </si>
-  <si>
-    <t>IDM FC.TISSUE 3X80'S</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>20128918</t>
+  </si>
+  <si>
+    <t>ISOPLUS COCO 350ML</t>
+  </si>
+  <si>
+    <t>20069773</t>
+  </si>
+  <si>
+    <t>ISOPLUS BTL 350ML</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>10004669</t>
+  </si>
+  <si>
+    <t>ULTRA UHT CHOCO 250M</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>10004668</t>
+  </si>
+  <si>
+    <t>ULTRA UHT STRAW 250M</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>10004443</t>
+  </si>
+  <si>
+    <t>INDOMILK UHT CKL 180</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20121662</t>
+  </si>
+  <si>
+    <t>INDOMLK KD LS CKL115</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20088789</t>
+  </si>
+  <si>
+    <t>INDOMLK KID F.CRM115</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>10004780</t>
+  </si>
+  <si>
+    <t>INDOMILK KID STRW115</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>20083775</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK HR.T 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>10006263</t>
+  </si>
+  <si>
+    <t>HEMAVITON ENERGY 150</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20133805</t>
+  </si>
+  <si>
+    <t>ENTRSL OLIVE STRL180</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20137159</t>
+  </si>
+  <si>
+    <t>TEH KOTAK MANGGA 300</t>
+  </si>
+  <si>
+    <t>20138376</t>
+  </si>
+  <si>
+    <t>BEBELAC 1 UHT 105ML</t>
+  </si>
+  <si>
+    <t>20124826</t>
+  </si>
+  <si>
+    <t>FAVOUR TISU WJH 120S</t>
   </si>
   <si>
     <t>RT</t>
   </si>
   <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20044199</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG CB.IJO85</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20009269</t>
-  </si>
-  <si>
-    <t>DELMONTE EXT.HOT 135</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20129436</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 RDANG132</t>
-  </si>
-  <si>
-    <t>20062365</t>
-  </si>
-  <si>
-    <t>SUKSES ISI2 A/KRM133</t>
-  </si>
-  <si>
-    <t>20066052</t>
-  </si>
-  <si>
-    <t>DLMONTE BBQ.SAUS 250</t>
-  </si>
-  <si>
-    <t>20066050</t>
-  </si>
-  <si>
-    <t>DELMONTE SPG.SAUS250</t>
-  </si>
-  <si>
-    <t>20134777</t>
-  </si>
-  <si>
-    <t>SASA KARI JPG ORI 40</t>
-  </si>
-  <si>
-    <t>10022118</t>
-  </si>
-  <si>
-    <t>SUN KARA SANTAN KL65</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20088712</t>
-  </si>
-  <si>
-    <t>SASA SANT.KLP CAIR65</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20132345</t>
-  </si>
-  <si>
-    <t>KELLOG FROT LOOPS 55</t>
-  </si>
-  <si>
-    <t>20134578</t>
-  </si>
-  <si>
-    <t>KELLOGGS COCO FILL60</t>
-  </si>
-  <si>
-    <t>20053052</t>
-  </si>
-  <si>
-    <t>CERES CHO.HZLNUT 180</t>
-  </si>
-  <si>
-    <t>20139438</t>
-  </si>
-  <si>
-    <t>DLMONTE CHO HZL 190G</t>
-  </si>
-  <si>
-    <t>20139437</t>
-  </si>
-  <si>
-    <t>DLMONTE PNUT BTR 170</t>
-  </si>
-  <si>
-    <t>20055265</t>
-  </si>
-  <si>
-    <t>T/J MADU TJ MRNI 150</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20126527</t>
-  </si>
-  <si>
-    <t>KEWPIE MAYO ORGNL 70</t>
-  </si>
-  <si>
-    <t>20003405</t>
-  </si>
-  <si>
-    <t>FORVITA MARGARINE200</t>
-  </si>
-  <si>
-    <t>20138100</t>
-  </si>
-  <si>
-    <t>FVTA MRGN TUB 200G</t>
-  </si>
-  <si>
-    <t>20132727</t>
-  </si>
-  <si>
-    <t>WNCHEZ KJ/CD OLH 170</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20103453</t>
-  </si>
-  <si>
-    <t>SAORI SAUS LD HTM133</t>
-  </si>
-  <si>
-    <t>20009973</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TERIYK135</t>
-  </si>
-  <si>
-    <t>20009966</t>
-  </si>
-  <si>
-    <t>SAORI SAUS TIRAM 133</t>
-  </si>
-  <si>
-    <t>20141464</t>
-  </si>
-  <si>
-    <t>RMN YES HKTA CHKN88G</t>
-  </si>
-  <si>
-    <t>20141466</t>
-  </si>
-  <si>
-    <t>RMN YES TKYO CHKN84G</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>10006890</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 40G</t>
+  </si>
+  <si>
+    <t>20028585</t>
+  </si>
+  <si>
+    <t>MI GEMEZ ENAK PREM22</t>
+  </si>
+  <si>
+    <t>10031595</t>
+  </si>
+  <si>
+    <t>ROMA BISC.KELAPA 300</t>
+  </si>
+  <si>
+    <t>20138030</t>
+  </si>
+  <si>
+    <t>JGOAN/N LOLY LDH WRN</t>
+  </si>
+  <si>
+    <t>20135627</t>
+  </si>
+  <si>
+    <t>MY BB H&amp;B WSH CLM375</t>
+  </si>
+  <si>
+    <t>20113916</t>
+  </si>
+  <si>
+    <t>MY BABY H&amp;B SWT 375</t>
+  </si>
+  <si>
+    <t>20103266</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C H&amp;F 180</t>
+  </si>
+  <si>
+    <t>20113915</t>
+  </si>
+  <si>
+    <t>MB KIDS S&amp;C SOFT 180</t>
+  </si>
+  <si>
+    <t>20113917</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC SWT 100</t>
+  </si>
+  <si>
+    <t>20135607</t>
+  </si>
+  <si>
+    <t>MB KIDS HBC LVELY100</t>
+  </si>
+  <si>
+    <t>20121430</t>
+  </si>
+  <si>
+    <t>SLEEK P/BTL,DOT 150</t>
+  </si>
+  <si>
+    <t>20071630</t>
+  </si>
+  <si>
+    <t>JOHNSON SHP SHNY 100</t>
   </si>
 </sst>
 </file>
@@ -631,17 +685,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,8 +716,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -677,11 +739,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -697,11 +759,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -717,11 +779,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -737,151 +799,151 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="H8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -892,256 +954,256 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H20" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1152,16 +1214,16 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>67</v>
       </c>
@@ -1172,73 +1234,253 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="H31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="E32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="H35" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="H36" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>22</v>
+      <c r="E37" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t/>
   </si>
@@ -685,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -693,11 +693,10 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -716,14 +715,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -739,11 +732,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -759,11 +752,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -779,11 +772,11 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -799,11 +792,11 @@
       <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -819,11 +812,11 @@
       <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -839,11 +832,11 @@
       <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -859,11 +852,11 @@
       <c r="E8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -879,11 +872,11 @@
       <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>26</v>
       </c>
@@ -899,11 +892,11 @@
       <c r="E10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -919,11 +912,11 @@
       <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F11" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
@@ -939,11 +932,11 @@
       <c r="E12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>35</v>
       </c>
@@ -959,11 +952,11 @@
       <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F13" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -979,11 +972,11 @@
       <c r="E14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -999,11 +992,11 @@
       <c r="E15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F15" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -1019,11 +1012,11 @@
       <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1039,11 +1032,11 @@
       <c r="E17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F17" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1059,11 +1052,11 @@
       <c r="E18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F18" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1079,11 +1072,11 @@
       <c r="E19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F19" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -1099,11 +1092,11 @@
       <c r="E20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
@@ -1119,11 +1112,11 @@
       <c r="E21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>57</v>
       </c>
@@ -1139,11 +1132,11 @@
       <c r="E22" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>59</v>
       </c>
@@ -1159,11 +1152,11 @@
       <c r="E23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
@@ -1179,11 +1172,11 @@
       <c r="E24" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>63</v>
       </c>
@@ -1199,11 +1192,11 @@
       <c r="E25" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>65</v>
       </c>
@@ -1219,11 +1212,11 @@
       <c r="E26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>67</v>
       </c>
@@ -1239,11 +1232,11 @@
       <c r="E27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>70</v>
       </c>
@@ -1259,11 +1252,11 @@
       <c r="E28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F28" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>72</v>
       </c>
@@ -1279,11 +1272,11 @@
       <c r="E29" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F29" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>74</v>
       </c>
@@ -1299,11 +1292,11 @@
       <c r="E30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F30" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>76</v>
       </c>
@@ -1319,11 +1312,11 @@
       <c r="E31" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F31" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>78</v>
       </c>
@@ -1339,11 +1332,11 @@
       <c r="E32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>80</v>
       </c>
@@ -1359,11 +1352,11 @@
       <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>82</v>
       </c>
@@ -1379,11 +1372,11 @@
       <c r="E34" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>84</v>
       </c>
@@ -1399,11 +1392,11 @@
       <c r="E35" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>86</v>
       </c>
@@ -1419,11 +1412,11 @@
       <c r="E36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>88</v>
       </c>
@@ -1439,11 +1432,11 @@
       <c r="E37" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>90</v>
       </c>
@@ -1459,11 +1452,11 @@
       <c r="E38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>92</v>
       </c>
@@ -1479,7 +1472,7 @@
       <c r="E39" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>56</v>
       </c>
     </row>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="88">
   <si>
     <t/>
   </si>
   <si>
-    <t>20126648</t>
-  </si>
-  <si>
-    <t>LE MINERALE 6X330ML</t>
+    <t>20034686</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW UBI 100</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -31,148 +31,241 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20122264</t>
+  </si>
+  <si>
+    <t>CHITATO MI GORENG 65</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20136587</t>
+  </si>
+  <si>
+    <t>POP MI INDOMIE GR 80</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20094171</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR 24X200</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMN YES HKTA CHKN88G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMN YES TKYO CHKN84G</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20121348</t>
+  </si>
+  <si>
+    <t>LASEGAR TWST J-L 320</t>
+  </si>
+  <si>
+    <t>20100143</t>
+  </si>
+  <si>
+    <t>TEH KOTAK APPLE 300</t>
+  </si>
+  <si>
+    <t>20087016</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LEMON 300</t>
+  </si>
+  <si>
+    <t>20135647</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LYCHEE 300</t>
+  </si>
+  <si>
+    <t>10004501</t>
+  </si>
+  <si>
+    <t>CC BIG BABOL BLUE20</t>
+  </si>
+  <si>
+    <t>10004503</t>
+  </si>
+  <si>
+    <t>CC BIG BABOL STRW.20</t>
+  </si>
+  <si>
+    <t>10036998</t>
+  </si>
+  <si>
+    <t>MENTOS MINT ROLL 37G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20059240</t>
+  </si>
+  <si>
+    <t>ANTANGIN JUNIOR 5'S</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20139596</t>
+  </si>
+  <si>
+    <t>PPSODNT SENSI EXP 60</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20128918</t>
-  </si>
-  <si>
-    <t>ISOPLUS COCO 350ML</t>
-  </si>
-  <si>
-    <t>20069773</t>
-  </si>
-  <si>
-    <t>ISOPLUS BTL 350ML</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20070569</t>
-  </si>
-  <si>
-    <t>INDOMLK BANANA 180</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>10004443</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CKL 180</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20121662</t>
-  </si>
-  <si>
-    <t>INDOMLK KD LS CKL115</t>
+    <t>20143274</t>
+  </si>
+  <si>
+    <t>PPSDNT PRCRE CPWHT90</t>
+  </si>
+  <si>
+    <t>20143275</t>
+  </si>
+  <si>
+    <t>PPSDNT PRCRE MPRTC90</t>
+  </si>
+  <si>
+    <t>20142679</t>
+  </si>
+  <si>
+    <t>PNTNE VIT INT BOND 5</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20088789</t>
-  </si>
-  <si>
-    <t>INDOMLK KID F.CRM115</t>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM COKLAT200</t>
+  </si>
+  <si>
+    <t>10008095</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM STRAW 200</t>
+  </si>
+  <si>
+    <t>20088964</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU TARO 200</t>
+  </si>
+  <si>
+    <t>20090189</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU KRML 200</t>
+  </si>
+  <si>
+    <t>20138895</t>
+  </si>
+  <si>
+    <t>ULTRA UHT BLUBRY 200</t>
+  </si>
+  <si>
+    <t>20032643</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT COK250</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
+  </si>
+  <si>
+    <t>20139300</t>
+  </si>
+  <si>
+    <t>BROOKFARM MATCHA 200</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>10004780</t>
-  </si>
-  <si>
-    <t>INDOMILK KID STRW115</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
+  </si>
+  <si>
+    <t>20142819</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 555ML</t>
+  </si>
+  <si>
+    <t>20142818</t>
+  </si>
+  <si>
+    <t>EWATER GRAPEFRT 555</t>
+  </si>
+  <si>
+    <t>20089821</t>
+  </si>
+  <si>
+    <t>ORONAMIN C DRINK 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
   </si>
   <si>
     <t>10006263</t>
@@ -182,117 +275,6 @@
   </si>
   <si>
     <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20133805</t>
-  </si>
-  <si>
-    <t>ENTRSL OLIVE STRL180</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20137159</t>
-  </si>
-  <si>
-    <t>TEH KOTAK MANGGA 300</t>
-  </si>
-  <si>
-    <t>20138376</t>
-  </si>
-  <si>
-    <t>BEBELAC 1 UHT 105ML</t>
-  </si>
-  <si>
-    <t>20124826</t>
-  </si>
-  <si>
-    <t>FAVOUR TISU WJH 120S</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>10006890</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 40G</t>
-  </si>
-  <si>
-    <t>20028585</t>
-  </si>
-  <si>
-    <t>MI GEMEZ ENAK PREM22</t>
-  </si>
-  <si>
-    <t>10031595</t>
-  </si>
-  <si>
-    <t>ROMA BISC.KELAPA 300</t>
-  </si>
-  <si>
-    <t>20138030</t>
-  </si>
-  <si>
-    <t>JGOAN/N LOLY LDH WRN</t>
-  </si>
-  <si>
-    <t>20135627</t>
-  </si>
-  <si>
-    <t>MY BB H&amp;B WSH CLM375</t>
-  </si>
-  <si>
-    <t>20113916</t>
-  </si>
-  <si>
-    <t>MY BABY H&amp;B SWT 375</t>
-  </si>
-  <si>
-    <t>20103266</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C H&amp;F 180</t>
-  </si>
-  <si>
-    <t>20113915</t>
-  </si>
-  <si>
-    <t>MB KIDS S&amp;C SOFT 180</t>
-  </si>
-  <si>
-    <t>20113917</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC SWT 100</t>
-  </si>
-  <si>
-    <t>20135607</t>
-  </si>
-  <si>
-    <t>MB KIDS HBC LVELY100</t>
-  </si>
-  <si>
-    <t>20121430</t>
-  </si>
-  <si>
-    <t>SLEEK P/BTL,DOT 150</t>
-  </si>
-  <si>
-    <t>20071630</t>
-  </si>
-  <si>
-    <t>JOHNSON SHP SHNY 100</t>
   </si>
 </sst>
 </file>
@@ -685,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -693,7 +675,7 @@
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -773,44 +755,44 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>5</v>
@@ -818,19 +800,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>5</v>
@@ -838,10 +820,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -850,18 +832,18 @@
         <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -870,7 +852,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>5</v>
@@ -878,10 +860,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -890,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>5</v>
@@ -910,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -918,10 +900,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -930,7 +912,7 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -938,10 +920,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -950,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -958,10 +940,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -970,7 +952,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -978,10 +960,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -990,18 +972,18 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1013,15 +995,15 @@
         <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1030,10 +1012,10 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1050,10 +1032,10 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1070,10 +1052,10 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1090,30 +1072,30 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1127,13 +1109,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1147,10 +1129,10 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1167,10 +1149,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1187,10 +1169,10 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1207,10 +1189,10 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1227,30 +1209,30 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1258,19 +1240,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1278,19 +1260,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1307,10 +1289,10 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1327,13 +1309,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1347,13 +1329,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1367,113 +1349,33 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20034686</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW UBI 100</t>
+    <t>10006651</t>
+  </si>
+  <si>
+    <t>VAPE FMK ORANGE 600</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,210 +28,213 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20124850</t>
+  </si>
+  <si>
+    <t>VAPE SPRY SWET PD600</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20122264</t>
-  </si>
-  <si>
-    <t>CHITATO MI GORENG 65</t>
+    <t>20120239</t>
+  </si>
+  <si>
+    <t>SHINZU'I KIREI 725ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20041399</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 380</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20138273</t>
+  </si>
+  <si>
+    <t>LRST BB.WIPE AF 2X50</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20135211</t>
+  </si>
+  <si>
+    <t>ZEN BW A.BAC SHIS380</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20142831</t>
+  </si>
+  <si>
+    <t>LUX BW FREESIA 300G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20141366</t>
+  </si>
+  <si>
+    <t>BARBER.D U/S FW 100</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20001061</t>
+  </si>
+  <si>
+    <t>MITU G/P PINK 2X50'S</t>
+  </si>
+  <si>
+    <t>20115153</t>
+  </si>
+  <si>
+    <t>KODOMO B.WIPE A/B50S</t>
+  </si>
+  <si>
+    <t>20137311</t>
+  </si>
+  <si>
+    <t>MY BBY KD KY PTH 150</t>
+  </si>
+  <si>
+    <t>20091440</t>
+  </si>
+  <si>
+    <t>CLEAR SHP MENTHOL160</t>
+  </si>
+  <si>
+    <t>20110117</t>
+  </si>
+  <si>
+    <t>G&amp;L FC.FOAM VIT.C100</t>
+  </si>
+  <si>
+    <t>10014293</t>
+  </si>
+  <si>
+    <t>POP MIE SOTO AYM 75G</t>
+  </si>
+  <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>20141464</t>
-  </si>
-  <si>
-    <t>RMN YES HKTA CHKN88G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20141466</t>
-  </si>
-  <si>
-    <t>RMN YES TKYO CHKN84G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20121348</t>
-  </si>
-  <si>
-    <t>LASEGAR TWST J-L 320</t>
-  </si>
-  <si>
-    <t>20100143</t>
-  </si>
-  <si>
-    <t>TEH KOTAK APPLE 300</t>
-  </si>
-  <si>
-    <t>20087016</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LEMON 300</t>
-  </si>
-  <si>
-    <t>20135647</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LYCHEE 300</t>
-  </si>
-  <si>
-    <t>10004501</t>
-  </si>
-  <si>
-    <t>CC BIG BABOL BLUE20</t>
-  </si>
-  <si>
-    <t>10004503</t>
-  </si>
-  <si>
-    <t>CC BIG BABOL STRW.20</t>
-  </si>
-  <si>
-    <t>10036998</t>
-  </si>
-  <si>
-    <t>MENTOS MINT ROLL 37G</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20059240</t>
-  </si>
-  <si>
-    <t>ANTANGIN JUNIOR 5'S</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20114021</t>
-  </si>
-  <si>
-    <t>IDM TISU WJH PRM 100</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>20139596</t>
-  </si>
-  <si>
-    <t>PPSODNT SENSI EXP 60</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20143274</t>
-  </si>
-  <si>
-    <t>PPSDNT PRCRE CPWHT90</t>
-  </si>
-  <si>
-    <t>20143275</t>
-  </si>
-  <si>
-    <t>PPSDNT PRCRE MPRTC90</t>
-  </si>
-  <si>
-    <t>20142679</t>
-  </si>
-  <si>
-    <t>PNTNE VIT INT BOND 5</t>
+    <t>20101859</t>
+  </si>
+  <si>
+    <t>SUNBAY EVP.MILK 380G</t>
+  </si>
+  <si>
+    <t>20052859</t>
+  </si>
+  <si>
+    <t>PRINGLES ORIGINAL 42</t>
+  </si>
+  <si>
+    <t>20073409</t>
+  </si>
+  <si>
+    <t>ROMA SANDW CKLT 157G</t>
+  </si>
+  <si>
+    <t>20066050</t>
+  </si>
+  <si>
+    <t>DELMONTE SPG.SAUS250</t>
+  </si>
+  <si>
+    <t>20099768</t>
+  </si>
+  <si>
+    <t>MAESTRO WJN SNGRA100</t>
+  </si>
+  <si>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>10007380</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM COKLAT200</t>
+  </si>
+  <si>
+    <t>10008095</t>
+  </si>
+  <si>
+    <t>ULTRA SLIM STRAW 200</t>
+  </si>
+  <si>
+    <t>20088964</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU TARO 200</t>
+  </si>
+  <si>
+    <t>20090189</t>
+  </si>
+  <si>
+    <t>ULTRA SUSU KRML 200</t>
+  </si>
+  <si>
+    <t>20138895</t>
+  </si>
+  <si>
+    <t>ULTRA UHT BLUBRY 200</t>
+  </si>
+  <si>
+    <t>20032643</t>
+  </si>
+  <si>
+    <t>ULTRA LOW FAT COK250</t>
+  </si>
+  <si>
+    <t>20139295</t>
+  </si>
+  <si>
+    <t>BROOKFARM ORI 200ML</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>10007380</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM COKLAT200</t>
-  </si>
-  <si>
-    <t>10008095</t>
-  </si>
-  <si>
-    <t>ULTRA SLIM STRAW 200</t>
-  </si>
-  <si>
-    <t>20088964</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU TARO 200</t>
-  </si>
-  <si>
-    <t>20090189</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU KRML 200</t>
-  </si>
-  <si>
-    <t>20138895</t>
-  </si>
-  <si>
-    <t>ULTRA UHT BLUBRY 200</t>
-  </si>
-  <si>
-    <t>20032643</t>
-  </si>
-  <si>
-    <t>ULTRA LOW FAT COK250</t>
-  </si>
-  <si>
-    <t>20139295</t>
-  </si>
-  <si>
-    <t>BROOKFARM ORI 200ML</t>
-  </si>
-  <si>
     <t>20139300</t>
   </si>
   <si>
@@ -272,9 +275,6 @@
   </si>
   <si>
     <t>HEMAVITON ENERGY 150</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
   </si>
 </sst>
 </file>
@@ -755,15 +755,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -772,18 +772,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -792,18 +792,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -812,58 +812,58 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -872,18 +872,18 @@
         <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -892,18 +892,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -912,18 +912,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -932,18 +932,18 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -952,38 +952,38 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -992,18 +992,18 @@
         <v>12</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1012,18 +1012,18 @@
         <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1032,18 +1032,18 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1052,18 +1052,18 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1072,10 +1072,10 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1089,13 +1089,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,13 +1109,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1129,13 +1129,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1149,13 +1149,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1169,13 +1169,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,13 +1209,13 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1229,13 +1229,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1249,133 +1249,133 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>87</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
